--- a/Sender Gmail Emails/Invitacion Curso Frank/Datos/Lista de Invitados.xlsx
+++ b/Sender Gmail Emails/Invitacion Curso Frank/Datos/Lista de Invitados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/CursoPLFrankPt2/Datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cinvestav365-my.sharepoint.com/personal/edgar_agustin_cinvestav_mx/Documents/Documentos/GitHub/Python/Sender Gmail Emails/Invitacion Curso Frank/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F11B224-9ACE-4D3B-8DA8-B3085A107215}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DD9760BC-8199-4F83-9FE3-50A275319245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB88D71A-08EE-48B9-9DF3-567B32EF65CE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57CD9F27-ED92-4D92-97BD-4EB2C2546C2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Asis_curso" sheetId="1" r:id="rId1"/>
@@ -2984,49 +2984,49 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Hipervínculo" xfId="42" builtinId="8"/>
+    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3041,12 +3041,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3363,15 +3359,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35E6767-67BF-4C43-BB50-257DECA7AA9D}">
   <dimension ref="A1:M1048573"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="40.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3409,7 +3405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46058.681250000001</v>
       </c>
@@ -3429,7 +3425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46045.55</v>
       </c>
@@ -3449,7 +3445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46055.72152777778</v>
       </c>
@@ -3472,7 +3468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045.674305555556</v>
       </c>
@@ -3492,7 +3488,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46267.284722222219</v>
       </c>
@@ -3512,7 +3508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>32</v>
       </c>
@@ -3529,7 +3525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46045.48541666667</v>
       </c>
@@ -3549,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -3569,7 +3565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46046.48541666667</v>
       </c>
@@ -3592,7 +3588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46045.727777777778</v>
       </c>
@@ -3615,7 +3611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46046.727777777778</v>
       </c>
@@ -3638,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -3658,7 +3654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46045.481944444444</v>
       </c>
@@ -3678,7 +3674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>61</v>
       </c>
@@ -3695,7 +3691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46045.51666666667</v>
       </c>
@@ -3718,7 +3714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46045.981249999997</v>
       </c>
@@ -3735,7 +3731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46046.447916666664</v>
       </c>
@@ -3758,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46056.543055555558</v>
       </c>
@@ -3778,7 +3774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46053.90625</v>
       </c>
@@ -3801,7 +3797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46058.82916666667</v>
       </c>
@@ -3824,7 +3820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46268.375694444447</v>
       </c>
@@ -3847,7 +3843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46053.855555555558</v>
       </c>
@@ -3864,7 +3860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46058.90902777778</v>
       </c>
@@ -3887,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46056.462500000001</v>
       </c>
@@ -3907,7 +3903,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46061.008333333331</v>
       </c>
@@ -3927,7 +3923,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -3947,7 +3943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46058.623611111114</v>
       </c>
@@ -3967,7 +3963,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46236.984027777777</v>
       </c>
@@ -3987,7 +3983,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>112</v>
       </c>
@@ -4004,7 +4000,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46053.932638888888</v>
       </c>
@@ -4021,7 +4017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46061.009722222225</v>
       </c>
@@ -4044,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46047.7</v>
       </c>
@@ -4067,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46058.683333333334</v>
       </c>
@@ -4090,7 +4086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46046.398611111108</v>
       </c>
@@ -4110,7 +4106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46053.84375</v>
       </c>
@@ -4130,7 +4126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46054.723611111112</v>
       </c>
@@ -4150,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46058.645833333336</v>
       </c>
@@ -4167,7 +4163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>142</v>
       </c>
@@ -4184,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -4204,7 +4200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46056.531944444447</v>
       </c>
@@ -4224,7 +4220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46048.751388888886</v>
       </c>
@@ -4244,7 +4240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46267.224999999999</v>
       </c>
@@ -4264,7 +4260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -4284,7 +4280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46061.975694444445</v>
       </c>
@@ -4304,7 +4300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46267.375694444447</v>
       </c>
@@ -4321,7 +4317,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46054.85</v>
       </c>
@@ -4338,7 +4334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46267.375694444447</v>
       </c>
@@ -4355,7 +4351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46048.472222222219</v>
       </c>
@@ -4372,7 +4368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46053.932638888888</v>
       </c>
@@ -4392,7 +4388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46046.425000000003</v>
       </c>
@@ -4412,7 +4408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -4432,7 +4428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46053.886805555558</v>
       </c>
@@ -4449,7 +4445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46048.505555555559</v>
       </c>
@@ -4469,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46058.695833333331</v>
       </c>
@@ -4489,7 +4485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46061.861805555556</v>
       </c>
@@ -4509,7 +4505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46053.8125</v>
       </c>
@@ -4529,7 +4525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46058.823611111111</v>
       </c>
@@ -4549,7 +4545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46045.487500000003</v>
       </c>
@@ -4569,7 +4565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46048.363888888889</v>
       </c>
@@ -4586,7 +4582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>198</v>
       </c>
@@ -4600,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46059.090277777781</v>
       </c>
@@ -4617,7 +4613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46046.707638888889</v>
       </c>
@@ -4634,7 +4630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46054.154166666667</v>
       </c>
@@ -4654,7 +4650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46045.484027777777</v>
       </c>
@@ -4674,7 +4670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46061.972916666666</v>
       </c>
@@ -4694,7 +4690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46045.51458333333</v>
       </c>
@@ -4711,7 +4707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46060.899305555555</v>
       </c>
@@ -4731,7 +4727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46045.590277777781</v>
       </c>
@@ -4748,7 +4744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46058.524305555555</v>
       </c>
@@ -4765,7 +4761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>227</v>
       </c>
@@ -4782,7 +4778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46045.750694444447</v>
       </c>
@@ -4799,7 +4795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46058.859722222223</v>
       </c>
@@ -4819,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46053.814583333333</v>
       </c>
@@ -4836,7 +4832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46045.5</v>
       </c>
@@ -4856,7 +4852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46053.893055555556</v>
       </c>
@@ -4876,7 +4872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>245</v>
       </c>
@@ -4890,7 +4886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46045.498611111114</v>
       </c>
@@ -4910,7 +4906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46058.416666666664</v>
       </c>
@@ -4930,7 +4926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46058.524305555555</v>
       </c>
@@ -4950,7 +4946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46057.824305555558</v>
       </c>
@@ -4967,7 +4963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -4987,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>263</v>
       </c>
@@ -5004,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46045.525000000001</v>
       </c>
@@ -5024,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46047.906944444447</v>
       </c>
@@ -5041,7 +5037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -5058,7 +5054,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46061.072916666664</v>
       </c>
@@ -5075,7 +5071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46061.442361111112</v>
       </c>
@@ -5095,7 +5091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46267.022222222222</v>
       </c>
@@ -5112,7 +5108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46053.87222222222</v>
       </c>
@@ -5132,7 +5128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46271.375694444447</v>
       </c>
@@ -5152,7 +5148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -5169,7 +5165,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46045.486111111109</v>
       </c>
@@ -5186,7 +5182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46059.474999999999</v>
       </c>
@@ -5206,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46061.685416666667</v>
       </c>
@@ -5226,7 +5222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46049.453472222223</v>
       </c>
@@ -5246,7 +5242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>304</v>
       </c>
@@ -5260,7 +5256,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46054.569444444445</v>
       </c>
@@ -5277,7 +5273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46061.363888888889</v>
       </c>
@@ -5294,7 +5290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>314</v>
       </c>
@@ -5308,7 +5304,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46052.765277777777</v>
       </c>
@@ -5325,7 +5321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46052.348611111112</v>
       </c>
@@ -5342,7 +5338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -5359,7 +5355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46058.405555555553</v>
       </c>
@@ -5379,7 +5375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46057.443749999999</v>
       </c>
@@ -5399,7 +5395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>331</v>
       </c>
@@ -5416,7 +5412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46045.520138888889</v>
       </c>
@@ -5433,7 +5429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46045.540972222225</v>
       </c>
@@ -5453,7 +5449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46055.317361111112</v>
       </c>
@@ -5470,7 +5466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46045.548611111109</v>
       </c>
@@ -5490,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46054.724999999999</v>
       </c>
@@ -5510,7 +5506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46061.609027777777</v>
       </c>
@@ -5527,7 +5523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46053.814583333333</v>
       </c>
@@ -5544,7 +5540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>352</v>
       </c>
@@ -5564,7 +5560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>355</v>
       </c>
@@ -5581,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -5601,7 +5597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46269.375694444447</v>
       </c>
@@ -5621,7 +5617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46053.88958333333</v>
       </c>
@@ -5638,7 +5634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46046.333333333336</v>
       </c>
@@ -5655,7 +5651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46061.563888888886</v>
       </c>
@@ -5675,7 +5671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46058.525000000001</v>
       </c>
@@ -5692,7 +5688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46272.375694444447</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46045.810416666667</v>
       </c>
@@ -5726,7 +5722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46273.375694444447</v>
       </c>
@@ -5746,7 +5742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46053.8125</v>
       </c>
@@ -5763,7 +5759,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>385</v>
       </c>
@@ -5777,7 +5773,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46057.667361111111</v>
       </c>
@@ -5794,7 +5790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46275.375694444447</v>
       </c>
@@ -5814,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46061.979166666664</v>
       </c>
@@ -5831,7 +5827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46045.479166666664</v>
       </c>
@@ -5848,7 +5844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46048.508333333331</v>
       </c>
@@ -5868,7 +5864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46058.782638888886</v>
       </c>
@@ -5888,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46061.915972222225</v>
       </c>
@@ -5905,7 +5901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46058.586805555555</v>
       </c>
@@ -5925,7 +5921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46054.70416666667</v>
       </c>
@@ -5945,7 +5941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46056.484027777777</v>
       </c>
@@ -5965,7 +5961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46045.490972222222</v>
       </c>
@@ -5982,7 +5978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46045.760416666664</v>
       </c>
@@ -6002,7 +5998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>422</v>
       </c>
@@ -6016,7 +6012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>426</v>
       </c>
@@ -6033,7 +6029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46058.65347222222</v>
       </c>
@@ -6053,7 +6049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46057.720833333333</v>
       </c>
@@ -6070,7 +6066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46045.477083333331</v>
       </c>
@@ -6087,7 +6083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46050.434027777781</v>
       </c>
@@ -6107,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46053.90347222222</v>
       </c>
@@ -6130,7 +6126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46060.9</v>
       </c>
@@ -6150,7 +6146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46054.001388888886</v>
       </c>
@@ -6170,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46061.070833333331</v>
       </c>
@@ -6187,7 +6183,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46059.894444444442</v>
       </c>
@@ -6204,7 +6200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46058.52847222222</v>
       </c>
@@ -6224,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46057.681944444441</v>
       </c>
@@ -6241,7 +6237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46050.825694444444</v>
       </c>
@@ -6261,7 +6257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46058.631249999999</v>
       </c>
@@ -6281,7 +6277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46046.84652777778</v>
       </c>
@@ -6298,7 +6294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46045.665277777778</v>
       </c>
@@ -6318,7 +6314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46061.665277777778</v>
       </c>
@@ -6335,7 +6331,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>477</v>
       </c>
@@ -6352,7 +6348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46060.944444444445</v>
       </c>
@@ -6372,7 +6368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46053.925694444442</v>
       </c>
@@ -6392,7 +6388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46049.59097222222</v>
       </c>
@@ -6409,7 +6405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46058.714583333334</v>
       </c>
@@ -6429,7 +6425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>492</v>
       </c>
@@ -6446,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46061.913888888892</v>
       </c>
@@ -6466,7 +6462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46054.587500000001</v>
       </c>
@@ -6483,7 +6479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>501</v>
       </c>
@@ -6500,7 +6496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>504</v>
       </c>
@@ -6517,7 +6513,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46267.45</v>
       </c>
@@ -6534,7 +6530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46054.402777777781</v>
       </c>
@@ -6551,7 +6547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46058.525000000001</v>
       </c>
@@ -6568,7 +6564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46045.490972222222</v>
       </c>
@@ -6588,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46047.944444444445</v>
       </c>
@@ -6608,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46049.425694444442</v>
       </c>
@@ -6628,7 +6624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>521</v>
       </c>
@@ -6642,7 +6638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46061.645138888889</v>
       </c>
@@ -6659,7 +6655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46045.509722222225</v>
       </c>
@@ -6676,7 +6672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>530</v>
       </c>
@@ -6693,7 +6689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46061.477777777778</v>
       </c>
@@ -6713,7 +6709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46045.495138888888</v>
       </c>
@@ -6733,7 +6729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46058.535416666666</v>
       </c>
@@ -6753,7 +6749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46045.53402777778</v>
       </c>
@@ -6770,7 +6766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46057.427777777775</v>
       </c>
@@ -6787,7 +6783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46054.956250000003</v>
       </c>
@@ -6804,7 +6800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46045.482638888891</v>
       </c>
@@ -6824,7 +6820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46047.510416666664</v>
       </c>
@@ -6841,7 +6837,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46048.482638888891</v>
       </c>
@@ -6858,7 +6854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46053.886111111111</v>
       </c>
@@ -6875,7 +6871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46061.354166666664</v>
       </c>
@@ -6895,7 +6891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46053.816666666666</v>
       </c>
@@ -6915,7 +6911,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46053.947916666664</v>
       </c>
@@ -6932,7 +6928,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46061.054861111108</v>
       </c>
@@ -6952,7 +6948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46058.520833333336</v>
       </c>
@@ -6969,7 +6965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46058.537499999999</v>
       </c>
@@ -6989,7 +6985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46046.049305555556</v>
       </c>
@@ -7006,7 +7002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46270.375694444447</v>
       </c>
@@ -7023,7 +7019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46267.304861111108</v>
       </c>
@@ -7043,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46053.940972222219</v>
       </c>
@@ -7060,7 +7056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46059.446527777778</v>
       </c>
@@ -7080,7 +7076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46061.826388888891</v>
       </c>
@@ -7100,7 +7096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46053.894444444442</v>
       </c>
@@ -7120,7 +7116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46058.756249999999</v>
       </c>
@@ -7137,7 +7133,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46059.551388888889</v>
       </c>
@@ -7157,7 +7153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46061.82708333333</v>
       </c>
@@ -7177,7 +7173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46061.97152777778</v>
       </c>
@@ -7197,7 +7193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46058.798611111109</v>
       </c>
@@ -7217,7 +7213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46045.5</v>
       </c>
@@ -7237,7 +7233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46061.47152777778</v>
       </c>
@@ -7254,7 +7250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46053.481249999997</v>
       </c>
@@ -7271,7 +7267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46045.490277777775</v>
       </c>
@@ -7291,7 +7287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>628</v>
       </c>
@@ -7308,7 +7304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46045.722222222219</v>
       </c>
@@ -7325,7 +7321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46045.496527777781</v>
       </c>
@@ -7342,7 +7338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46045.481249999997</v>
       </c>
@@ -7362,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46061.01458333333</v>
       </c>
@@ -7379,7 +7375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46054.102777777778</v>
       </c>
@@ -7396,7 +7392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>646</v>
       </c>
@@ -7410,7 +7406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46274.375694444447</v>
       </c>
@@ -7430,7 +7426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46048.520138888889</v>
       </c>
@@ -7450,7 +7446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46058.523611111108</v>
       </c>
@@ -7473,7 +7469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46048.508333333331</v>
       </c>
@@ -7496,7 +7492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46056.454861111109</v>
       </c>
@@ -7519,7 +7515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46059.527083333334</v>
       </c>
@@ -7539,7 +7535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46058.688194444447</v>
       </c>
@@ -7556,7 +7552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46045.498611111114</v>
       </c>
@@ -7579,7 +7575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46058.897916666669</v>
       </c>
@@ -7602,7 +7598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46046.476388888892</v>
       </c>
@@ -7622,7 +7618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46045.477777777778</v>
       </c>
@@ -7639,7 +7635,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46045.50277777778</v>
       </c>
@@ -7659,7 +7655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46058.656944444447</v>
       </c>
@@ -7679,7 +7675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>692</v>
       </c>
@@ -7699,7 +7695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46267.276388888888</v>
       </c>
@@ -7709,7 +7705,7 @@
       <c r="C230" t="s">
         <v>697</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D230" s="2" t="s">
         <v>698</v>
       </c>
       <c r="E230" t="s">
@@ -7722,7 +7718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46059.396527777775</v>
       </c>
@@ -7742,7 +7738,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46045.486111111109</v>
       </c>
@@ -7762,7 +7758,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46045.484027777777</v>
       </c>
@@ -7782,7 +7778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46047.488888888889</v>
       </c>
@@ -7802,7 +7798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46053.929861111108</v>
       </c>
@@ -7825,7 +7821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46058.978472222225</v>
       </c>
@@ -7848,7 +7844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46058.655555555553</v>
       </c>
@@ -7868,7 +7864,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46267.370138888888</v>
       </c>
@@ -7888,7 +7884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46057.644444444442</v>
       </c>
@@ -7911,7 +7907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46058.65625</v>
       </c>
@@ -7934,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46055.651388888888</v>
       </c>
@@ -7957,7 +7953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46058.657638888886</v>
       </c>
@@ -7977,7 +7973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>741</v>
       </c>
@@ -7991,7 +7987,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>744</v>
       </c>
@@ -8005,7 +8001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46236.995138888888</v>
       </c>
@@ -8028,7 +8024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46045.486805555556</v>
       </c>
@@ -8051,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46045.48333333333</v>
       </c>
@@ -8071,7 +8067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46045.874305555553</v>
       </c>
@@ -8091,7 +8087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46045.741666666669</v>
       </c>
@@ -8114,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46056.272916666669</v>
       </c>
@@ -8134,7 +8130,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>767</v>
       </c>
@@ -8154,7 +8150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46060.165972222225</v>
       </c>
@@ -8177,7 +8173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46049.572916666664</v>
       </c>
@@ -8194,7 +8190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46053.948611111111</v>
       </c>
@@ -8214,7 +8210,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46058.525694444441</v>
       </c>
@@ -8237,7 +8233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>785</v>
       </c>
@@ -8260,7 +8256,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46053.813194444447</v>
       </c>
@@ -8283,7 +8279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46061.484027777777</v>
       </c>
@@ -8306,7 +8302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46060.685416666667</v>
       </c>
@@ -8329,7 +8325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46058.661111111112</v>
       </c>
@@ -8352,7 +8348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46053.862500000003</v>
       </c>
@@ -8375,7 +8371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46060.566666666666</v>
       </c>
@@ -8398,7 +8394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46061.265972222223</v>
       </c>
@@ -8421,7 +8417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>813</v>
       </c>
@@ -8441,7 +8437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>224</v>
       </c>
@@ -8461,7 +8457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>275</v>
       </c>
@@ -8481,7 +8477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1048573" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="1048573" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E1048573" t="s">
         <v>22</v>
       </c>
@@ -8489,6 +8485,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D264" r:id="rId1" xr:uid="{43A79DF7-27C1-4F27-9D47-74D1FF01C7AD}"/>
+    <hyperlink ref="D230" r:id="rId2" xr:uid="{B9A96F6A-BA66-42D3-84E1-1E6D9D5DBB6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
